--- a/AAII_Financials/Quarterly/BRK.B_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRK.B_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>BRK.B</t>
   </si>
@@ -656,216 +656,228 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>101808000</v>
+      </c>
+      <c r="E8" s="3">
         <v>93675000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>94232000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>94972000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>92515000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>89725000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>94916000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>92995000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>93653000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>89869000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>93376000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>93210000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>92503000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>85393000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>78072000</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9628000</v>
+      </c>
+      <c r="E9" s="3">
         <v>9096000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9078000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9556000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9036000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8810000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9397000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9415000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9434000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9046000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>-26737000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>23376000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23362000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18878000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9663000</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>33150000</v>
+      </c>
+      <c r="E10" s="3">
         <v>13444000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>31055000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>39036000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20748000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6279000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24591000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33500000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>39115000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>16529000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>47702000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-15961000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>46173000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>45282000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>22343000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -883,8 +895,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -930,8 +943,11 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -977,8 +993,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1024,55 +1043,61 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3606000</v>
+      </c>
+      <c r="E15" s="3">
         <v>3510000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3549000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3333000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3329000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3265000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3283000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3206000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3198000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3168000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3129000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3210000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3096000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3051000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2758000</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1087,102 +1112,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>68658000</v>
+      </c>
+      <c r="E17" s="3">
         <v>80231000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>63177000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>55936000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>71767000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>83446000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>70325000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>59495000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54538000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>73340000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>45674000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>109171000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46330000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40111000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>55729000</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>33150000</v>
+      </c>
+      <c r="E18" s="3">
         <v>13444000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>31055000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>39036000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20748000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6279000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24591000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>33500000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>39115000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16529000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>47702000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15961000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>46173000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>45282000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>22343000</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1200,243 +1232,259 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-176000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5301000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-330000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4745000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-126000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-874000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-222000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-252000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-493000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-512000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-262000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-511000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-688000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-905000</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>37004000</v>
+      </c>
+      <c r="E21" s="3">
         <v>17130000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>29303000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>42699000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>19332000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9670000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>28748000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>36928000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>42565000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20190000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>51343000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12489000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>49780000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>49021000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>26006000</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1335000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1301000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1298000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1261000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1253000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1257000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1440000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1214000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1230000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1316000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1276000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1260000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1249000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1218000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1139000</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32063000</v>
+      </c>
+      <c r="E23" s="3">
         <v>12319000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>24456000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>38105000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14750000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5148000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24025000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>32508000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>38137000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15706000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>46938000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16959000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>45435000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>44752000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>22109000</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6291000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2140000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5189000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7241000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2293000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>476000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4274000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6028000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7639000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2874000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9180000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4392000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9236000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8995000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3872000</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1482,102 +1530,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>25772000</v>
+      </c>
+      <c r="E26" s="3">
         <v>10179000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19267000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>30864000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12457000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4672000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19751000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>26480000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>30498000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12832000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>37758000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12567000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>36199000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>35757000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18237000</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>25667000</v>
+      </c>
+      <c r="E27" s="3">
         <v>10106000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19199000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>30796000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12370000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4603000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19694000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>26251000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>30348000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12702000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>37574000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12767000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>35912000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>35504000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18080000</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1623,8 +1680,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1670,8 +1730,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1717,8 +1780,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1764,102 +1830,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>248000</v>
+      </c>
+      <c r="E32" s="3">
         <v>176000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5301000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>330000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4745000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>126000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>874000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>222000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>252000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>493000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>512000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>262000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>511000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>688000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>905000</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>25667000</v>
+      </c>
+      <c r="E33" s="3">
         <v>10106000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19199000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>30796000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12370000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4603000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19694000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26251000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>30348000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12702000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>37574000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12767000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>35912000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35504000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18080000</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1905,107 +1980,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>25667000</v>
+      </c>
+      <c r="E35" s="3">
         <v>10106000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19199000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>30796000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12370000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4603000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19694000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26251000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>30348000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12702000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>37574000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12767000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>35912000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35504000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18080000</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2023,8 +2107,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2042,196 +2127,209 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40609000</v>
+      </c>
+      <c r="E41" s="3">
         <v>58122000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>51877000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>76306000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100486000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>42180000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>47729000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37181000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42324000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35549000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>38022000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30840000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>50055000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26747000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35811000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>324905000</v>
+      </c>
+      <c r="E42" s="3">
         <v>339261000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>321434000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>305367000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>243605000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>305501000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>286472000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>288031000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>234618000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>153444000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>129619000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>126401000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>97322000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>103869000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>92774000</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>53197000</v>
+      </c>
+      <c r="E43" s="3">
         <v>51759000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>48718000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>53460000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>51796000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>51692000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>48390000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>52046000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>52469000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>52835000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>51260000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>52726000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>51657000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>52488000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>48285000</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>29975000</v>
+      </c>
+      <c r="E44" s="3">
         <v>28723000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>27624000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>28519000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>27471000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>27034000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>27008000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>27617000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>27798000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>27770000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>25856000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>24755000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>25295000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>25499000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>25366000</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2241,232 +2339,247 @@
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>184000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>197000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>186000</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>292000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>241000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>238000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>334000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>470000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>355000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>504000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>589000</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>449437000</v>
+      </c>
+      <c r="E46" s="3">
         <v>478553000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>450345000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>464483000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>424297000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>427268000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>410246000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>405978000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>358197000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>270447000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>245712000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>235956000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>225282000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>209658000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>203413000</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>360761000</v>
+      </c>
+      <c r="E47" s="3">
         <v>325654000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>335572000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>326708000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>308330000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>309914000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>318086000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>317825000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>331738000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>382616000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>406666000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>368552000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>403255000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>377130000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>361971000</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>244136000</v>
+      </c>
+      <c r="E48" s="3">
         <v>241744000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>241180000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>230565000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>227863000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>224758000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>228772000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>222272000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>219469000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>217500000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>221870000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>211498000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>209188000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>205855000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>201940000</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>118108000</v>
+      </c>
+      <c r="E49" s="3">
         <v>118467000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>117916000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>119643000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>119421000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>119448000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>119654000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>120852000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>120767000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>121298000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>121766000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>122856000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>123519000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>122148000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>108598000</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2512,8 +2625,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2559,55 +2675,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>52230000</v>
+      </c>
+      <c r="E52" s="3">
         <v>49900000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>34423000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>46939000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>46861000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>46385000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>35928000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>44333000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>43540000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>43421000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35188000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>47797000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>47345000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>49438000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>35665000</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2653,55 +2775,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1263071000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1252271000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1222176000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1225963000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1163968000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1164532000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1153881000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1147251000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1108860000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1070035000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1069978000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1019933000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1041573000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>997072000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>948465000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2719,8 +2847,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2738,290 +2867,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>61846000</v>
+      </c>
+      <c r="E57" s="3">
         <v>58215000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>50979000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>56817000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>55152000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>54762000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>49719000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>56247000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>53316000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>51937000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>49351000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>54879000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>51924000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>52238000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>44635000</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2663000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2243000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11219000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3039000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2986000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1921000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3929000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2024000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2254000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2658000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6757000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2524000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3066000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3517000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3712000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>90947000</v>
+      </c>
+      <c r="E59" s="3">
         <v>105914000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1525000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>110771000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>83209000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>100626000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15076000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>107221000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>101695000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>95946000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>878000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>85991000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>93320000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>86493000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1193000</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>155456000</v>
+      </c>
+      <c r="E60" s="3">
         <v>166372000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>63723000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>170627000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>141347000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>157309000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>68724000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>165492000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>157265000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>150541000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>56986000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>143394000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>148310000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>142248000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>49540000</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>125936000</v>
+      </c>
+      <c r="E61" s="3">
         <v>126643000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>124152000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>124204000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>124034000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>124006000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>126829000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>122483000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>121374000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>120096000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>126813000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>122257000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>122281000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>120107000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>123971000</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>198748000</v>
+      </c>
+      <c r="E62" s="3">
         <v>197053000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>197662000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>197208000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>195897000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>194169000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>192302000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>194473000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>190065000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>189638000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>192558000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>187641000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>188048000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>188098000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>188199000</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3067,8 +3215,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3114,8 +3265,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3161,55 +3315,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>512894000</v>
+      </c>
+      <c r="E66" s="3">
         <v>522821000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>502473000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>525522000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>493692000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>507790000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>502226000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>515445000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>500889000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>492250000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>499208000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>485206000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>489812000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>480812000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>466784000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3227,8 +3387,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3274,8 +3435,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3321,8 +3485,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3368,8 +3535,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3415,55 +3585,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>798959000</v>
+      </c>
+      <c r="E72" s="3">
         <v>773292000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>763186000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>743987000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>713191000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>700821000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>696218000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>676524000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>650273000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>619925000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>607350000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>569776000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>582543000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>546631000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>511127000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3509,8 +3685,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3556,8 +3735,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3603,55 +3785,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>747910000</v>
+      </c>
+      <c r="E76" s="3">
         <v>727181000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>717419000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>698155000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>667989000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>654471000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>649368000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>629069000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>601697000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>571490000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>561273000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>525330000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>539883000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>504554000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>473424000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3697,107 +3885,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>25667000</v>
+      </c>
+      <c r="E81" s="3">
         <v>10106000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19199000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>30796000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12370000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4603000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19694000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26251000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>30348000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12702000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>37574000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12767000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>35912000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35504000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18080000</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3815,55 +4012,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2910000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2821000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2783000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2798000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2741000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2733000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2629000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2782000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2653000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2622000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2430000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2425000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2411000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2400000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2395000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3909,8 +4110,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3956,8 +4160,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4003,8 +4210,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4050,8 +4260,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4097,55 +4310,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11215000</v>
+      </c>
+      <c r="E89" s="3">
         <v>10438000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11192000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13789000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10085000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10903000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4621000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1803000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13602000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10566000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14400000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13669000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12434000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8693000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10311000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4163,55 +4382,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5645000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4986000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6202000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5586000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4858000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4281000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5347000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4701000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4535000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4393000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5708000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5303000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4685000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3713000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4557000</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4257,8 +4480,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4304,55 +4530,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24336000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4308000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-38392000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-39052000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>49358000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16401000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4268000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3904000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7448000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3203000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7351000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28048000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>10655000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7919000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6092000</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4370,8 +4602,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4417,8 +4650,11 @@
       <c r="Q96" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4464,8 +4700,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4511,8 +4750,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4558,145 +4800,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4283000</v>
+      </c>
+      <c r="E100" s="3">
         <v>174000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2511000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>835000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1166000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>53000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1653000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3065000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>854000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9802000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-136000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4636000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>289000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9922000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1351000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-76000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-158000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>87000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-97000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-44000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>126000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-34000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-23000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>47000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>175000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-296000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-326000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>53000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>103000</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17450000</v>
+      </c>
+      <c r="E102" s="3">
         <v>6241000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-24542000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-24117000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>58373000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5521000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10384000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5079000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6911000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2483000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7039000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19049000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23355000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9101000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3043000</v>
       </c>
     </row>
